--- a/차입금_이자원금_상환스케줄_전북신협광주.xlsx
+++ b/차입금_이자원금_상환스케줄_전북신협광주.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -705,7 +705,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>광주 1220</t>
+          <t>광주 274781</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>광주 1220</t>
+          <t>광주 274781</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>광주 1220</t>
+          <t>광주 274781</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>광주 1220</t>
+          <t>광주 274781</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>광주 1220</t>
+          <t>광주 274781</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>광주 1220</t>
+          <t>광주 274781</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 3781411</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>전북 1071</t>
+          <t>전북 6831557</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr"/>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>신협 212</t>
+          <t>신협 616173</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr"/>
